--- a/2026_Lunarworkshop_presentation.xlsx
+++ b/2026_Lunarworkshop_presentation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="239" documentId="8_{48C49700-4057-4E5A-A4EA-ECE4EC1E6A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2354DEE9-B2FF-476D-8764-403D66235F82}"/>
+  <xr:revisionPtr revIDLastSave="260" documentId="8_{48C49700-4057-4E5A-A4EA-ECE4EC1E6A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79E5A2EC-592E-4699-91B5-CA55CD5E059E}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="121">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -236,6 +236,267 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Landing Site Selection of Pit Craters for the Lunar Landing Mission</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달 토양의 입자 크기에 따른 편광 특성 실험 연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달 토양의 입자 크기와 최대 편광도 간의 관계를 조사하기 위해 입도별 아폴로 샘플의 선형 편광도를 측정하였다. 실험 결과, 입자 크기가 증가함에 따라 최대 편광도가 증가하는 경향이 나타났다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달 탐사용 자기장 측정기 개발 현황</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달 자기장 관측은 달 내부 구조, 자기이상지역의 기원, 태양풍과 달 표면의 상호작용을 이해하기 위한 핵심 기술이다. 경희대학교는 국내 최초의 달 탐사선 다누리 (KPLO)에 탑재된 자기장 측정기 (KMAG)를 개발하여 성공적인 달 궤도 자기장 관측을 수행하였으며, 획득된 자료를 기반으로 달 자기장 지도 구축과 다양한 과학 연구를 수행하고 있다. 또한 NASA CLPS (Commercial Lunar Payload Services) 미션을 위한 후보 탑재체로써 달 착륙선용 자기장 측정기를 개발하여 착륙 지점의 국소 자기장 및 우주환경 측정을 위한 기반 기술을 확보하였다. 현재는 향후 유인 달 탐사를 위한 달 표면 전개형 자기장 측정기를 개발하고 있다. 본 발표에서는 다누리 궤도선 자기장 측정기와 CLPS 달 착륙선 자기장 측정기의 개발 과정 및 운용 현황과 유인 우주탐사를 위한 자기장 측정기 개발 현황에 대해 소개한다.</t>
+  </si>
+  <si>
+    <t>달 표면에서의 자기장 측정은 Apollo 시대 LSM으로 시작되어 오랜 공백을 거쳐 Blue Ghost LMS 임무로 다시 이어지고 있다. 본 발표에서는 지금까지의 달 표면 자기장 미션들을 소개하고, 이 데이터들을 활용해 현재 진행 중인 연구 내용을 공유한다. 아울러 이를 바탕으로 향후 달 자기장 탐사에 있어 표면-궤도 동시 관측 및 다지점 표면 관측의 필요성을 논의한다.</t>
+  </si>
+  <si>
+    <t>달 표면 자기장 탐사 및 과학적 연구: Apollo LSM에서 Blue Ghost LMS까지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다 탑재체 데이터 활용 착륙지 안전도 사전 분석 방법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>선종호 (경희대학교)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>설우형 (한국천문연구원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이덕행 (한국천문연구원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백슬민 (한국천문연구원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박필재 (한국전자통신연구원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>송영주 (경희대학교)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이은지 (한국천문연구원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이준현 (한국천문연구원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김세린 (한국천문연구원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정민섭 (한국천문연구원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김관혁 (경희대학교)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>윤동석 (경희대학교)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>홍예원 (경희대학교)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박현후 (경희대학교)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조우인 (경희대학교)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김상화 (경희대학교)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진호 (경희대학교)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신현진 (한국항공우주연구원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>초청: 달탐사 계획과 추진 방향</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박진혜 (우주항공청)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달 탐사용 초소형관측기기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13:45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>양륜관 (KAIST)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>09:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>09:45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다누리 자기장 측정기 KMAG를 이용한 달 내부 구조 연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다누리가 달 궤도 상에서 성공적으로 과학 임무를 수행하고 있다. 이러한 임무를 수행하기 위해 고려된 기계적인 형상에 대한 특징을 소개하며, 각 탑재체의 배치에 대한 개념도 소개하고자 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달 탐사 착륙지 선정에 있어서 과학탐사 목표와 함께 고려 하여야하는 착륙지 안전도 분석에 대하여 논의한다. 착륙지의 안전도 분석을 위한 수학적 틀을 제시하고 다중 탑재체 데이터 활용 방법을 모색한다. 이를 위한 탑재체 LRO - NAC, LOLA, SLDEM, Diviner, miniRF 데이터를 고려하였다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달 우주환경 관측을 위한 저에너지 정전기 분석기(ESA) 기술 개발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>본 연구에서는 차세대 우주탐사를 위한 저에너지 정전기 분석기(ESA) 기술 개발 현황을 소개한다. ESA는 수십 eV에서 수십 keV 범위의 저에너지 하전입자를 측정하여 달 주변 플라즈마 및 우주환경을 연구하는 핵심 장비이다. 한국천문연구원에서는 ESA의 국내 개발을 위해 핵심 기술을 확보하고 시제품 제작 및 성능 검증을 수행하고 있으며, 향후 달 및 행성 탐사 임무 적용을 위한 기술 기반 구축을 목표로 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>본 발표에서는 Intuitive Machines IM-3 착륙선에 탑재되어 달 표면의 대전 입자를 측정할 예정인 Lunar Space Environment Monitor (LUSEM)의 초기 운용 계획과 데이터 해석 준비 현황을 소개한다. LUSEM은 발사 6시간 후 전원이 인가되어 운용을 시작하며, 달 표면 착륙 시점까지 항행 단계 전반에 걸쳐 지속적인 관측을 수행한다. 이에 따라 비행 단계에서의 안정적인 장비 제어 및 데이터 수집을 위한 초기 운용 시나리오를 수립하였으며, 관측된 대전 입자 데이터를 신속하고 정밀하게 분석하기 위한 선제적 해석 체계를 준비중이다. 본 초기 운용 계획은 항행 및 착륙 과정에서 수집되는 우주 환경 데이터의 신뢰성을 확보하고, 향후 성공적인 달 표면 관측 임무를 수행하는 데 핵심적인 기여를 할 것으로 기대한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지속적인 달 탐사 및 향후 유·무인 임무의 확대에 따라 달 표면뿐만 아니라 착륙 과정까지 연속적인 위치·항법·시각(PNT) 정보를 제공할 수 있는 독립적인 달 항법 인프라의 필요성이 증가하고 있다. 본 연구에서는 극지역 장기 체류에 유리한 ELFO와 달 전역 커버리지를 위한 CFO를 결합한 혼합 위성군을 구성하고, 달 전역 표면 및 Powered Descent 구간을 대상으로 PDOP 기반 항법 성능을 평가한다. 또한 위성 수와 PDOP Availability 간의 상충관계를 고려한 다목적 최적화를 통해, 달 전역 탐사와 착륙 임무에 걸맞는 효율적인 Lunar PNT 위성군 설계 방안을 제시한다.</t>
+  </si>
+  <si>
     <r>
       <t>Kaguya observed rapid energy fluctuations, varying by a factor of ~10 within a few minutes, during passages near the subsolar region (SEL latitude -30° to 40°, longitude -5° to 5</t>
     </r>
@@ -263,261 +524,995 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Landing Site Selection of Pit Craters for the Lunar Landing Mission</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>달 토양의 입자 크기에 따른 편광 특성 실험 연구</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>달 토양의 입자 크기와 최대 편광도 간의 관계를 조사하기 위해 입도별 아폴로 샘플의 선형 편광도를 측정하였다. 실험 결과, 입자 크기가 증가함에 따라 최대 편광도가 증가하는 경향이 나타났다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>s13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>17:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11:15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>달 탐사용 자기장 측정기 개발 현황</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>달 자기장 관측은 달 내부 구조, 자기이상지역의 기원, 태양풍과 달 표면의 상호작용을 이해하기 위한 핵심 기술이다. 경희대학교는 국내 최초의 달 탐사선 다누리 (KPLO)에 탑재된 자기장 측정기 (KMAG)를 개발하여 성공적인 달 궤도 자기장 관측을 수행하였으며, 획득된 자료를 기반으로 달 자기장 지도 구축과 다양한 과학 연구를 수행하고 있다. 또한 NASA CLPS (Commercial Lunar Payload Services) 미션을 위한 후보 탑재체로써 달 착륙선용 자기장 측정기를 개발하여 착륙 지점의 국소 자기장 및 우주환경 측정을 위한 기반 기술을 확보하였다. 현재는 향후 유인 달 탐사를 위한 달 표면 전개형 자기장 측정기를 개발하고 있다. 본 발표에서는 다누리 궤도선 자기장 측정기와 CLPS 달 착륙선 자기장 측정기의 개발 과정 및 운용 현황과 유인 우주탐사를 위한 자기장 측정기 개발 현황에 대해 소개한다.</t>
-  </si>
-  <si>
-    <t>달 표면에서의 자기장 측정은 Apollo 시대 LSM으로 시작되어 오랜 공백을 거쳐 Blue Ghost LMS 임무로 다시 이어지고 있다. 본 발표에서는 지금까지의 달 표면 자기장 미션들을 소개하고, 이 데이터들을 활용해 현재 진행 중인 연구 내용을 공유한다. 아울러 이를 바탕으로 향후 달 자기장 탐사에 있어 표면-궤도 동시 관측 및 다지점 표면 관측의 필요성을 논의한다.</t>
-  </si>
-  <si>
-    <t>달 표면 자기장 탐사 및 과학적 연구: Apollo LSM에서 Blue Ghost LMS까지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>s18</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>다 탑재체 데이터 활용 착륙지 안전도 사전 분석 방법</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>선종호 (경희대학교)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>설우형 (한국천문연구원)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이덕행 (한국천문연구원)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>백슬민 (한국천문연구원)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>박필재 (한국전자통신연구원)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>송영주 (경희대학교)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이은지 (한국천문연구원)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이준현 (한국천문연구원)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>김세린 (한국천문연구원)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>정민섭 (한국천문연구원)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>김관혁 (경희대학교)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>윤동석 (경희대학교)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>홍예원 (경희대학교)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>박현후 (경희대학교)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>조우인 (경희대학교)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>김상화 (경희대학교)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>진호 (경희대학교)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>신현진 (한국항공우주연구원)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14:45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15:45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>s19</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>초청: 달탐사 계획과 추진 방향</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>박진혜 (우주항공청)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>달 탐사용 초소형관측기기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13:45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14:15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15:15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16:45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>17:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>17:15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>s20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>양륜관 (KAIST)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">ELFO-CFO Hybrid Constellation Design for Global Lunar PNT Including Powered Descent </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>09:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>09:45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10:15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10:45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11:45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>다누리 자기장 측정기 KMAG를 이용한 달 내부 구조 연구</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>다누리가 달 궤도 상에서 성공적으로 과학 임무를 수행하고 있다. 이러한 임무를 수행하기 위해 고려된 기계적인 형상에 대한 특징을 소개하며, 각 탑재체의 배치에 대한 개념도 소개하고자 한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>달 탐사 착륙지 선정에 있어서 과학탐사 목표와 함께 고려 하여야하는 착륙지 안전도 분석에 대하여 논의한다. 착륙지의 안전도 분석을 위한 수학적 틀을 제시하고 다중 탑재체 데이터 활용 방법을 모색한다. 이를 위한 탑재체 LRO - NAC, LOLA, SLDEM, Diviner, miniRF 데이터를 고려하였다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>달 우주환경 관측을 위한 저에너지 정전기 분석기(ESA) 기술 개발</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>본 연구에서는 차세대 우주탐사를 위한 저에너지 정전기 분석기(ESA) 기술 개발 현황을 소개한다. ESA는 수십 eV에서 수십 keV 범위의 저에너지 하전입자를 측정하여 달 주변 플라즈마 및 우주환경을 연구하는 핵심 장비이다. 한국천문연구원에서는 ESA의 국내 개발을 위해 핵심 기술을 확보하고 시제품 제작 및 성능 검증을 수행하고 있으며, 향후 달 및 행성 탐사 임무 적용을 위한 기술 기반 구축을 목표로 한다.</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>향후</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>달</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탐사는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>단일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탐사선</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>중심에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>항법</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>통신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>서비스를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제공하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인프라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탐사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>체계로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>발전할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>것으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>예상된다. 본</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>발표에서는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>달</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>항법</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>통신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위성군</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구축을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>요구조건과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>달</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>궤도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>환경의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>특수성을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>살펴보고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>각종</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>후보</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>궤도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아키텍처의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장단점을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비교한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>또한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>운용을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>궤도결정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>궤도유지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>궤도력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>등</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비행역학</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>운용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전략의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>중요성을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>논의한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>태양풍 입자가 지구 앞 활 충격파에 튕겨 나오며 태양 쪽으로 퍼지는 '상류파'를 세 위성(KPLO, ARTEMIS-P1/P2)이 동시 관측했습니다. 활 충격파에 가까운 위성에서 먼저 감지되어 태양 방향 전파가 확인됐고, 속도는 600~1000 km/s로 알펜속도보다 훨씬 빠르기 때문에 단순 대류만으로는 설명하기 어렵습니다. 이는 파동 고유의 전파 성분을 시사하며, 상류파의 생성 및 전파 메커니즘 이해에 중요한 단서를 제공합니다.</t>
+  </si>
+  <si>
+    <t>ELFO-CFO Hybrid Constellation Design for Global Lunar PNT Including Powered Descent (Powered Descent를 포함한 달 전역 PNT용 ELFO-CFO 혼합 위성군)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>본 발표는 우리나라의 달탐사 계획과 앞으로의 방향성에 대한 초청 발표로, 20분의 발표 및 10분의 질의응답 시간으로 준비되어 있습니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -525,7 +1520,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -548,19 +1543,47 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -577,14 +1600,23 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -925,7 +1957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FAA5805-02C0-4AE9-B5DF-E91EE7468B4D}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="5" width="9" style="1"/>
@@ -934,7 +1966,7 @@
     <col min="8" max="8" width="15.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -959,14 +1991,17 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -977,10 +2012,10 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -989,13 +2024,17 @@
         <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>26</v>
       </c>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1006,10 +2045,10 @@
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -1018,10 +2057,17 @@
         <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>65</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1032,25 +2078,36 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="H4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1061,25 +2118,29 @@
         <v>12</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I6" t="s">
-        <v>115</v>
-      </c>
+      <c r="G6" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -1090,22 +2151,27 @@
         <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H7" t="s">
-        <v>70</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -1116,25 +2182,36 @@
         <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="I8" t="s">
-        <v>113</v>
-      </c>
+      <c r="G8" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -1145,22 +2222,29 @@
         <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F10" t="s">
         <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="H10" t="s">
-        <v>101</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -1171,25 +2255,29 @@
         <v>12</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I11" t="s">
-        <v>112</v>
-      </c>
+      <c r="H11" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1200,22 +2288,36 @@
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F12" t="s">
         <v>17</v>
       </c>
       <c r="G12" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" t="s">
         <v>87</v>
       </c>
-      <c r="H12" t="s">
-        <v>88</v>
-      </c>
+      <c r="I12" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1226,10 +2328,10 @@
         <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="F14" t="s">
         <v>15</v>
@@ -1238,10 +2340,17 @@
         <v>42</v>
       </c>
       <c r="H14" t="s">
-        <v>71</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="I14" t="s">
+        <v>118</v>
+      </c>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -1252,25 +2361,29 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="F15" t="s">
         <v>15</v>
       </c>
       <c r="G15" t="s">
+        <v>51</v>
+      </c>
+      <c r="H15" t="s">
+        <v>71</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="H15" t="s">
-        <v>72</v>
-      </c>
-      <c r="I15" t="s">
-        <v>53</v>
-      </c>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -1281,10 +2394,10 @@
         <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F16" t="s">
         <v>40</v>
@@ -1293,15 +2406,26 @@
         <v>43</v>
       </c>
       <c r="H16" t="s">
-        <v>73</v>
-      </c>
-      <c r="I16" t="s">
+        <v>72</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>44</v>
       </c>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B18" t="s">
         <v>22</v>
@@ -1310,10 +2434,10 @@
         <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F18" t="s">
         <v>40</v>
@@ -1322,13 +2446,17 @@
         <v>45</v>
       </c>
       <c r="H18" t="s">
-        <v>74</v>
-      </c>
-      <c r="I18" t="s">
+        <v>73</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>46</v>
       </c>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>35</v>
       </c>
@@ -1339,7 +2467,7 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>31</v>
@@ -1351,13 +2479,17 @@
         <v>49</v>
       </c>
       <c r="H19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I19" t="s">
-        <v>50</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -1371,7 +2503,7 @@
         <v>31</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F20" t="s">
         <v>15</v>
@@ -1380,13 +2512,17 @@
         <v>48</v>
       </c>
       <c r="H20" t="s">
-        <v>76</v>
-      </c>
-      <c r="I20" t="s">
+        <v>75</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>37</v>
       </c>
@@ -1397,10 +2533,10 @@
         <v>12</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F21" t="s">
         <v>17</v>
@@ -1409,10 +2545,24 @@
         <v>41</v>
       </c>
       <c r="H21" t="s">
-        <v>69</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -1423,27 +2573,31 @@
         <v>12</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F23" t="s">
         <v>16</v>
       </c>
       <c r="G23" t="s">
+        <v>57</v>
+      </c>
+      <c r="H23" t="s">
+        <v>76</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H23" t="s">
-        <v>77</v>
-      </c>
-      <c r="I23" t="s">
-        <v>59</v>
-      </c>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B24" t="s">
         <v>22</v>
@@ -1452,24 +2606,29 @@
         <v>12</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F24" t="s">
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H24" t="s">
-        <v>78</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B25" t="s">
         <v>22</v>
@@ -1478,27 +2637,31 @@
         <v>12</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F25" t="s">
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H25" t="s">
-        <v>79</v>
-      </c>
-      <c r="I25" t="s">
-        <v>60</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B26" t="s">
         <v>22</v>
@@ -1507,23 +2670,27 @@
         <v>12</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F26" t="s">
         <v>16</v>
       </c>
       <c r="G26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s">
-        <v>80</v>
-      </c>
-      <c r="I26" t="s">
+        <v>79</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>21</v>
       </c>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/2026_Lunarworkshop_presentation.xlsx
+++ b/2026_Lunarworkshop_presentation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="260" documentId="8_{48C49700-4057-4E5A-A4EA-ECE4EC1E6A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79E5A2EC-592E-4699-91B5-CA55CD5E059E}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="8_{CDA25B47-9413-4463-A930-48A48A6A6572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF3A7C82-DCE4-4DA4-BE92-DF8FF856AEB9}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="115">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -154,14 +154,6 @@
   </si>
   <si>
     <t>s9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>IM-5 달 착륙선용 우주 방사선 검출기인 LVRAD의 개요 (Overview of LVRAD: A Space Radiation Detector for the IM-5 Lunar Lander)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LVRAD(Lunar Vehicle RAdiation Dosimeter)는 달 표면 방사선 환경 관측을 위해 개발된 한국천문연구원(KASI) 주도 탑재체이다. 본 탑재체는 NASA CLPS(민간 달 탑재체 서비스) 계획의 일환으로 Intuitive Machines사의 IM-5 착륙선에 탑재되어 2030년 발사될 예정이다. LVRAD의 주 임무는 달 표면의 방사선 환경을 측정하고 생물학적 영향 평가를 위한 선량 지표를 산출하는 것이며, 부차 임무로서 열 및 열외 중성자 측정을 통한 지하 얼음(물) 증거 탐색과 감마선 분광 분석을 통한 표면 방사성 물질 분석을 수행한다. 본 발표에서는 LVRAD의 과학적 임무 목적과 함께, 이를 수행하기 위한 시스템 구성 모듈 및 하드웨어 설계에 대해 소개하고자 한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -252,14 +244,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>16:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>17:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>11:15</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -294,10 +278,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이덕행 (한국천문연구원)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>백슬민 (한국천문연구원)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -362,18 +342,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>14:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>14:45</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>15:45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>s19</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -414,26 +386,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>16:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16:45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>17:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>17:15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>s20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>양륜관 (KAIST)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1513,6 +1465,30 @@
   </si>
   <si>
     <t>본 발표는 우리나라의 달탐사 계획과 앞으로의 방향성에 대한 초청 발표로, 20분의 발표 및 10분의 질의응답 시간으로 준비되어 있습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:55</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17:10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17:25</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1520,7 +1496,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1542,14 +1518,6 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1600,23 +1568,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1957,7 +1919,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FAA5805-02C0-4AE9-B5DF-E91EE7468B4D}">
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="5" width="9" style="1"/>
@@ -1966,7 +1928,7 @@
     <col min="8" max="8" width="15.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1991,17 +1953,14 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -2012,10 +1971,10 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -2024,17 +1983,13 @@
         <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>63</v>
-      </c>
-      <c r="I2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I2" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -2045,10 +2000,10 @@
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -2057,17 +2012,13 @@
         <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>64</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
+        <v>60</v>
+      </c>
+      <c r="I3" t="s">
+        <v>102</v>
+      </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -2078,36 +2029,25 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
+      <c r="G4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I4" t="s">
+        <v>101</v>
+      </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -2118,29 +2058,22 @@
         <v>12</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="G6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" t="s">
+        <v>64</v>
+      </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -2151,27 +2084,25 @@
         <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="I7" t="s">
+        <v>99</v>
+      </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -2182,36 +2113,25 @@
         <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>67</v>
+      <c r="G8" t="s">
+        <v>107</v>
+      </c>
+      <c r="H8" t="s">
+        <v>88</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
+        <v>103</v>
+      </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -2222,29 +2142,25 @@
         <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>119</v>
+        <v>37</v>
       </c>
       <c r="H10" t="s">
-        <v>100</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="I10" t="s">
+        <v>98</v>
+      </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -2255,71 +2171,56 @@
         <v>12</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" t="s">
         <v>80</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
+      <c r="I11" t="s">
+        <v>108</v>
+      </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>28</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>11</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C13" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F12" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" t="s">
-        <v>86</v>
-      </c>
-      <c r="H12" t="s">
-        <v>87</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
+      <c r="D13" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13" t="s">
+        <v>65</v>
+      </c>
+      <c r="I13" t="s">
+        <v>106</v>
+      </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
@@ -2328,31 +2229,27 @@
         <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="F14" t="s">
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="H14" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I14" t="s">
-        <v>118</v>
-      </c>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
+        <v>50</v>
+      </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
         <v>11</v>
@@ -2361,71 +2258,56 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G15" t="s">
+        <v>41</v>
+      </c>
+      <c r="H15" t="s">
+        <v>67</v>
+      </c>
+      <c r="I15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F17" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17" t="s">
+        <v>68</v>
+      </c>
+      <c r="I17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>51</v>
-      </c>
-      <c r="H15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16" t="s">
-        <v>40</v>
-      </c>
-      <c r="G16" t="s">
-        <v>43</v>
-      </c>
-      <c r="H16" t="s">
-        <v>72</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>53</v>
       </c>
       <c r="B18" t="s">
         <v>22</v>
@@ -2434,31 +2316,27 @@
         <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="F18" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H18" t="s">
-        <v>73</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="I18" t="s">
+        <v>104</v>
+      </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
@@ -2467,31 +2345,27 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="F19" t="s">
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H19" t="s">
-        <v>74</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="I19" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
         <v>22</v>
@@ -2500,71 +2374,56 @@
         <v>12</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F20" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G20" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="H20" t="s">
-        <v>75</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
+        <v>63</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>105</v>
+      </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" t="s">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" t="s">
         <v>22</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C22" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F21" t="s">
-        <v>17</v>
-      </c>
-      <c r="G21" t="s">
-        <v>41</v>
-      </c>
-      <c r="H21" t="s">
-        <v>68</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
+      <c r="D22" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" t="s">
+        <v>53</v>
+      </c>
+      <c r="H22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I22" t="s">
+        <v>54</v>
+      </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
         <v>22</v>
@@ -2573,31 +2432,24 @@
         <v>12</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="F23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G23" t="s">
+        <v>97</v>
+      </c>
+      <c r="H23" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>57</v>
-      </c>
-      <c r="H23" t="s">
-        <v>76</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>61</v>
       </c>
       <c r="B24" t="s">
         <v>22</v>
@@ -2606,29 +2458,27 @@
         <v>12</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="F24" t="s">
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="H24" t="s">
-        <v>77</v>
-      </c>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="I24" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B25" t="s">
         <v>22</v>
@@ -2637,60 +2487,23 @@
         <v>12</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="F25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G25" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s">
-        <v>78</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>99</v>
-      </c>
-      <c r="B26" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G26" t="s">
-        <v>88</v>
-      </c>
-      <c r="H26" t="s">
-        <v>79</v>
-      </c>
-      <c r="I26" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I25" t="s">
         <v>21</v>
       </c>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/2026_Lunarworkshop_presentation.xlsx
+++ b/2026_Lunarworkshop_presentation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="8_{CDA25B47-9413-4463-A930-48A48A6A6572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF3A7C82-DCE4-4DA4-BE92-DF8FF856AEB9}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{7C337711-845B-48E8-9B2F-7D4F6183F691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD91B70C-DF3A-4961-8FC0-44FCBADAE4D1}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="116">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -134,10 +134,6 @@
   </si>
   <si>
     <t>s6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>s7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -342,6 +338,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>14:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>14:45</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -386,6 +386,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>s20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>양륜관 (KAIST)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1476,19 +1480,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>16:55</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16:40</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>17:10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>17:25</t>
+    <t>16:35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17:05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17:20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1596,10 +1600,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1971,7 +1971,7 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>82</v>
@@ -1980,13 +1980,13 @@
         <v>16</v>
       </c>
       <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I2" t="s">
         <v>25</v>
-      </c>
-      <c r="H2" t="s">
-        <v>59</v>
-      </c>
-      <c r="I2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -2012,10 +2012,10 @@
         <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -2038,13 +2038,13 @@
         <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -2058,19 +2058,19 @@
         <v>12</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="F6" t="s">
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -2093,13 +2093,13 @@
         <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -2122,18 +2122,18 @@
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
@@ -2145,19 +2145,19 @@
         <v>87</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -2171,10 +2171,10 @@
         <v>12</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F11" t="s">
         <v>17</v>
@@ -2186,12 +2186,12 @@
         <v>80</v>
       </c>
       <c r="I11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>
@@ -2203,19 +2203,19 @@
         <v>112</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F13" t="s">
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -2229,22 +2229,22 @@
         <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F14" t="s">
         <v>15</v>
       </c>
       <c r="G14" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" t="s">
+        <v>65</v>
+      </c>
+      <c r="I14" t="s">
         <v>49</v>
-      </c>
-      <c r="H14" t="s">
-        <v>66</v>
-      </c>
-      <c r="I14" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -2258,27 +2258,27 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G15" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15" t="s">
+        <v>66</v>
+      </c>
+      <c r="I15" t="s">
         <v>41</v>
-      </c>
-      <c r="H15" t="s">
-        <v>67</v>
-      </c>
-      <c r="I15" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
@@ -2287,27 +2287,27 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G17" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" t="s">
+        <v>67</v>
+      </c>
+      <c r="I17" t="s">
         <v>43</v>
-      </c>
-      <c r="H17" t="s">
-        <v>68</v>
-      </c>
-      <c r="I17" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
         <v>22</v>
@@ -2316,22 +2316,22 @@
         <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F18" t="s">
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -2345,22 +2345,22 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F19" t="s">
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -2374,22 +2374,22 @@
         <v>12</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F20" t="s">
         <v>17</v>
       </c>
       <c r="G20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -2403,27 +2403,27 @@
         <v>12</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F22" t="s">
         <v>16</v>
       </c>
       <c r="G22" t="s">
+        <v>52</v>
+      </c>
+      <c r="H22" t="s">
+        <v>70</v>
+      </c>
+      <c r="I22" t="s">
         <v>53</v>
-      </c>
-      <c r="H22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I22" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="B23" t="s">
         <v>22</v>
@@ -2432,24 +2432,24 @@
         <v>12</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F23" t="s">
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="B24" t="s">
         <v>22</v>
@@ -2458,27 +2458,27 @@
         <v>12</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F24" t="s">
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B25" t="s">
         <v>22</v>
@@ -2487,10 +2487,10 @@
         <v>12</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F25" t="s">
         <v>16</v>
@@ -2499,7 +2499,7 @@
         <v>81</v>
       </c>
       <c r="H25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I25" t="s">
         <v>21</v>

--- a/2026_Lunarworkshop_presentation.xlsx
+++ b/2026_Lunarworkshop_presentation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{7C337711-845B-48E8-9B2F-7D4F6183F691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD91B70C-DF3A-4961-8FC0-44FCBADAE4D1}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{7C337711-845B-48E8-9B2F-7D4F6183F691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C73C1CE1-0354-416D-9901-ED2E5CF6371F}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="117">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -209,10 +209,6 @@
   </si>
   <si>
     <t>Using Kaguya data, we statistically investigated the spatial distribution and dynamics of lunar ions when the Moon was in the terrestrial magnetotail lobes. These ions were observed on the dayside at altitudes of 30–120 km, with energies of ~50-1000 eV. Because they originate from neutral particles in the lunar exosphere or at the surface, their analysis provides a valuable diagnostic of the neutral particle distribution. To examine the origin and distribution of these ions, we performed test-particle simulations of lunar ions generated at the surface and in the exosphere. The results show that the spatial distribution of lunar ions observed at spacecraft altitudes is not globally uniform relative to the underlying exosphere, but is instead concentrated over the Procellarum KREEP Terrane (PKT). Both observations and simulations indicate that the PKT region serves as a major source of lunar ions at spacecraft altitudes.</t>
-  </si>
-  <si>
-    <t>Some lunar crustal magnetic anomalies are associated with albedo markings known as swirls; however, the processes governing their formation remain unclear. In this study, we focus on Reiner Gamma, a well-studied lunar anomaly and a key site for investigating the relationship between albedo patterns and magnetic anomalies. We perform test-particle simulations to examine how the Reiner Gamma swirl interacts with the local magnetic field, employing incident solar wind particles with energies of 0.5–1.0 keV and both line and disk magnetization models. The simulated magnetic fields are comparable to observations from previous lunar orbiters at altitudes of approximately 20 km and 40 km. Their maximum and minimum intensities, corresponding respectively to bright lobes and dark cusps on the lunar surface, align with the optical albedo patterns observed at Reiner Gamma. Our simulations show that the reflection area of solar wind particles above Reiner Gamma increases as the incident solar wind energy decreases. In the bright lobes, solar wind particle reflection exhibits a clear dependence on strong horizontal magnetic fields and dominant perpendicular energies. In contrast, reflection in the cusps is less definitive, being additionally governed by the interplay between relative perpendicular energy and magnetic configuration. We discuss the necessary conditions under which incident solar wind particles are absorbed at the surface or reflected above Reiner Gamma.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Interaction Between Solar Wind Particles and the Reiner Gamma Magnetic Anomaly: Observations and Test-Particle Simulations</t>
@@ -1493,6 +1489,14 @@
   </si>
   <si>
     <t>17:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KMAG는 외부 자기장 변동에 대한 달 내부의 유도 자기장 응답을 분석하여 전기전도도 구조를 추정하는 전자기 탐사 기법을, 아폴로 시대 달 앞면 탐사에 이어 달 뒷면에 최초로 적용하였다. 이를 바탕으로 달 내부 구조와 진화 과정에 대한 새로운 제약 조건을 제시한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lunar magnetic anomalies are often associated with albedo markings known as lunar swirls, yet the processes governing their formation remain unresolved. In this study, we investigate the Reiner Gamma magnetic anomaly using test-particle simulations with solar wind particles and different magnetization models to examine the relationship between the local magnetic field structure and solar wind particle reflection. Based on the simulation results, we identify the conditions under which incident solar wind particles are reflected above lunar magnetic anomalies.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1500,7 +1504,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1549,6 +1553,22 @@
       <name val="Arial"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1572,7 +1592,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1583,6 +1603,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1600,6 +1626,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1971,10 +2001,10 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -1983,7 +2013,7 @@
         <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I2" t="s">
         <v>25</v>
@@ -2000,10 +2030,10 @@
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -2012,10 +2042,10 @@
         <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -2029,22 +2059,22 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
       <c r="G4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I4" t="s">
         <v>101</v>
-      </c>
-      <c r="H4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I4" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -2058,19 +2088,19 @@
         <v>12</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="F6" t="s">
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -2084,22 +2114,22 @@
         <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -2113,22 +2143,22 @@
         <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -2142,10 +2172,10 @@
         <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
@@ -2154,10 +2184,10 @@
         <v>36</v>
       </c>
       <c r="H10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -2171,22 +2201,22 @@
         <v>12</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="F11" t="s">
         <v>17</v>
       </c>
       <c r="G11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H11" t="s">
         <v>79</v>
       </c>
-      <c r="H11" t="s">
-        <v>80</v>
-      </c>
       <c r="I11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -2200,10 +2230,10 @@
         <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="F13" t="s">
         <v>15</v>
@@ -2212,10 +2242,10 @@
         <v>39</v>
       </c>
       <c r="H13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -2229,22 +2259,22 @@
         <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="F14" t="s">
         <v>15</v>
       </c>
       <c r="G14" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14" t="s">
+        <v>64</v>
+      </c>
+      <c r="I14" t="s">
         <v>48</v>
-      </c>
-      <c r="H14" t="s">
-        <v>65</v>
-      </c>
-      <c r="I14" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -2258,10 +2288,10 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="F15" t="s">
         <v>37</v>
@@ -2270,7 +2300,7 @@
         <v>40</v>
       </c>
       <c r="H15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I15" t="s">
         <v>41</v>
@@ -2278,7 +2308,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
@@ -2287,10 +2317,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="F17" t="s">
         <v>37</v>
@@ -2299,7 +2329,7 @@
         <v>42</v>
       </c>
       <c r="H17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I17" t="s">
         <v>43</v>
@@ -2316,7 +2346,7 @@
         <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>28</v>
@@ -2325,13 +2355,13 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -2348,19 +2378,19 @@
         <v>28</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F19" t="s">
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I19" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -2374,10 +2404,10 @@
         <v>12</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="F20" t="s">
         <v>17</v>
@@ -2386,10 +2416,10 @@
         <v>38</v>
       </c>
       <c r="H20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -2403,27 +2433,27 @@
         <v>12</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="F22" t="s">
         <v>16</v>
       </c>
       <c r="G22" t="s">
+        <v>51</v>
+      </c>
+      <c r="H22" t="s">
+        <v>69</v>
+      </c>
+      <c r="I22" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="H22" t="s">
-        <v>70</v>
-      </c>
-      <c r="I22" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B23" t="s">
         <v>22</v>
@@ -2432,24 +2462,27 @@
         <v>12</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H23" t="s">
-        <v>71</v>
+        <v>70</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B24" t="s">
         <v>22</v>
@@ -2458,27 +2491,27 @@
         <v>12</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F24" t="s">
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H24" t="s">
-        <v>72</v>
-      </c>
-      <c r="I24" t="s">
-        <v>54</v>
+        <v>71</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B25" t="s">
         <v>22</v>
@@ -2487,21 +2520,21 @@
         <v>12</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="F25" t="s">
         <v>16</v>
       </c>
       <c r="G25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s">
-        <v>73</v>
-      </c>
-      <c r="I25" t="s">
+        <v>72</v>
+      </c>
+      <c r="I25" s="4" t="s">
         <v>21</v>
       </c>
     </row>

--- a/2026_Lunarworkshop_presentation.xlsx
+++ b/2026_Lunarworkshop_presentation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{7C337711-845B-48E8-9B2F-7D4F6183F691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C73C1CE1-0354-416D-9901-ED2E5CF6371F}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="8_{7C337711-845B-48E8-9B2F-7D4F6183F691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF352910-F38F-40D2-81B6-2240BAE5B213}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="120">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -378,10 +378,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>15:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>s20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -426,10 +422,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>다누리가 달 궤도 상에서 성공적으로 과학 임무를 수행하고 있다. 이러한 임무를 수행하기 위해 고려된 기계적인 형상에 대한 특징을 소개하며, 각 탑재체의 배치에 대한 개념도 소개하고자 한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>달 탐사 착륙지 선정에 있어서 과학탐사 목표와 함께 고려 하여야하는 착륙지 안전도 분석에 대하여 논의한다. 착륙지의 안전도 분석을 위한 수학적 틀을 제시하고 다중 탑재체 데이터 활용 방법을 모색한다. 이를 위한 탑재체 LRO - NAC, LOLA, SLDEM, Diviner, miniRF 데이터를 고려하였다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1468,35 +1460,55 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>15:50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16:20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16:35</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16:50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>17:05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>17:20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>KMAG는 외부 자기장 변동에 대한 달 내부의 유도 자기장 응답을 분석하여 전기전도도 구조를 추정하는 전자기 탐사 기법을, 아폴로 시대 달 앞면 탐사에 이어 달 뒷면에 최초로 적용하였다. 이를 바탕으로 달 내부 구조와 진화 과정에 대한 새로운 제약 조건을 제시한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Lunar magnetic anomalies are often associated with albedo markings known as lunar swirls, yet the processes governing their formation remain unresolved. In this study, we investigate the Reiner Gamma magnetic anomaly using test-particle simulations with solar wind particles and different magnetization models to examine the relationship between the local magnetic field structure and solar wind particle reflection. Based on the simulation results, we identify the conditions under which incident solar wind particles are reflected above lunar magnetic anomalies.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>초청: 달착륙선 착륙후보지역 착륙적합성 분석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김동규(한국항공우주연구원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">032년 발사되는 달착륙선(Korea Pathfinder Lunar Landr, KPLL)의 착륙후보지역에 대하여 착륙 및 운영 적합성 분석 작업 현황과 향후 수행 업무 등을 발표하고자 합니다. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:55</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17:10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17:25</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1949,7 +1961,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FAA5805-02C0-4AE9-B5DF-E91EE7468B4D}">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="5" width="9" style="1"/>
@@ -2045,7 +2057,7 @@
         <v>58</v>
       </c>
       <c r="I3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -2068,13 +2080,13 @@
         <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H4" t="s">
         <v>59</v>
       </c>
       <c r="I4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -2129,7 +2141,7 @@
         <v>60</v>
       </c>
       <c r="I7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -2152,14 +2164,17 @@
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>103</v>
-      </c>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -2172,22 +2187,22 @@
         <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>109</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="H10" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="I10" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -2204,48 +2219,45 @@
         <v>109</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" t="s">
+        <v>36</v>
+      </c>
+      <c r="H11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" t="s">
         <v>110</v>
       </c>
-      <c r="F11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" t="s">
-        <v>78</v>
-      </c>
-      <c r="H11" t="s">
-        <v>79</v>
-      </c>
-      <c r="I11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="H12" t="s">
         <v>111</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="I12" t="s">
         <v>112</v>
-      </c>
-      <c r="F13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" t="s">
-        <v>39</v>
-      </c>
-      <c r="H13" t="s">
-        <v>63</v>
-      </c>
-      <c r="I13" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -2259,22 +2271,22 @@
         <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F14" t="s">
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="H14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I14" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -2288,51 +2300,51 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" t="s">
+        <v>64</v>
+      </c>
+      <c r="I15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F16" t="s">
         <v>37</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G16" t="s">
         <v>40</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H16" t="s">
         <v>65</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I16" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>49</v>
-      </c>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F17" t="s">
-        <v>37</v>
-      </c>
-      <c r="G17" t="s">
-        <v>42</v>
-      </c>
-      <c r="H17" t="s">
-        <v>66</v>
-      </c>
-      <c r="I17" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -2346,22 +2358,22 @@
         <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="F18" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="G18" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I18" t="s">
-        <v>104</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -2375,22 +2387,22 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="F19" t="s">
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I19" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -2404,51 +2416,51 @@
         <v>12</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" t="s">
+        <v>44</v>
+      </c>
+      <c r="H20" t="s">
+        <v>68</v>
+      </c>
+      <c r="I20" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="F21" t="s">
         <v>17</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G21" t="s">
         <v>38</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H21" t="s">
         <v>61</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F22" t="s">
-        <v>16</v>
-      </c>
-      <c r="G22" t="s">
-        <v>51</v>
-      </c>
-      <c r="H22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>52</v>
+      <c r="I21" s="3" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
@@ -2462,22 +2474,22 @@
         <v>12</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="F23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G23" t="s">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="H23" t="s">
-        <v>70</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>115</v>
+        <v>69</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
@@ -2491,27 +2503,27 @@
         <v>12</v>
       </c>
       <c r="D24" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="F24" t="s">
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="H24" t="s">
-        <v>71</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>53</v>
+        <v>70</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B25" t="s">
         <v>22</v>
@@ -2520,21 +2532,50 @@
         <v>12</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F25" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" t="s">
+        <v>54</v>
+      </c>
+      <c r="H25" t="s">
+        <v>71</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>113</v>
+      </c>
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="F26" t="s">
         <v>16</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G26" t="s">
         <v>80</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H26" t="s">
         <v>72</v>
       </c>
-      <c r="I25" s="4" t="s">
+      <c r="I26" s="4" t="s">
         <v>21</v>
       </c>
     </row>

--- a/2026_Lunarworkshop_presentation.xlsx
+++ b/2026_Lunarworkshop_presentation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="8_{7C337711-845B-48E8-9B2F-7D4F6183F691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF352910-F38F-40D2-81B6-2240BAE5B213}"/>
+  <xr:revisionPtr revIDLastSave="149" documentId="8_{7C337711-845B-48E8-9B2F-7D4F6183F691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83F26221-8E36-4525-8B1A-FEE7E01BE19D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="121">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -330,18 +330,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>13:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14:45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>s19</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -358,26 +346,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>13:45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14:15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15:15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>s20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1509,6 +1477,42 @@
   </si>
   <si>
     <t>17:25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13:35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:05</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2013,10 +2017,10 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -2042,10 +2046,10 @@
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -2057,7 +2061,7 @@
         <v>58</v>
       </c>
       <c r="I3" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -2071,22 +2075,22 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="H4" t="s">
         <v>59</v>
       </c>
       <c r="I4" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -2100,10 +2104,10 @@
         <v>12</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="F6" t="s">
         <v>17</v>
@@ -2126,10 +2130,10 @@
         <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
@@ -2141,7 +2145,7 @@
         <v>60</v>
       </c>
       <c r="I7" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -2155,22 +2159,22 @@
         <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H8" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -2187,22 +2191,22 @@
         <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F10" t="s">
         <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I10" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -2216,10 +2220,10 @@
         <v>12</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
@@ -2242,22 +2246,22 @@
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="F12" t="s">
         <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H12" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="I12" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -2271,10 +2275,10 @@
         <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="F14" t="s">
         <v>15</v>
@@ -2286,7 +2290,7 @@
         <v>63</v>
       </c>
       <c r="I14" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -2300,10 +2304,10 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="F15" t="s">
         <v>15</v>
@@ -2329,10 +2333,10 @@
         <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="F16" t="s">
         <v>37</v>
@@ -2358,10 +2362,10 @@
         <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="F18" t="s">
         <v>37</v>
@@ -2387,7 +2391,7 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>28</v>
@@ -2402,7 +2406,7 @@
         <v>67</v>
       </c>
       <c r="I19" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -2419,7 +2423,7 @@
         <v>28</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F20" t="s">
         <v>15</v>
@@ -2431,7 +2435,7 @@
         <v>68</v>
       </c>
       <c r="I20" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -2445,10 +2449,10 @@
         <v>12</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F21" t="s">
         <v>17</v>
@@ -2460,7 +2464,7 @@
         <v>61</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
@@ -2474,10 +2478,10 @@
         <v>12</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F23" t="s">
         <v>16</v>
@@ -2494,7 +2498,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B24" t="s">
         <v>22</v>
@@ -2503,7 +2507,7 @@
         <v>12</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>50</v>
@@ -2512,18 +2516,18 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s">
         <v>70</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B25" t="s">
         <v>22</v>
@@ -2535,7 +2539,7 @@
         <v>50</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="F25" t="s">
         <v>15</v>
@@ -2552,7 +2556,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B26" t="s">
         <v>22</v>
@@ -2561,16 +2565,16 @@
         <v>12</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F26" t="s">
         <v>16</v>
       </c>
       <c r="G26" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H26" t="s">
         <v>72</v>

--- a/2026_Lunarworkshop_presentation.xlsx
+++ b/2026_Lunarworkshop_presentation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="149" documentId="8_{7C337711-845B-48E8-9B2F-7D4F6183F691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83F26221-8E36-4525-8B1A-FEE7E01BE19D}"/>
+  <xr:revisionPtr revIDLastSave="151" documentId="8_{7C337711-845B-48E8-9B2F-7D4F6183F691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F741CD8-B016-4935-BEB4-B6F75B3D2666}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="122">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1448,10 +1448,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">032년 발사되는 달착륙선(Korea Pathfinder Lunar Landr, KPLL)의 착륙후보지역에 대하여 착륙 및 운영 적합성 분석 작업 현황과 향후 수행 업무 등을 발표하고자 합니다. </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>s21</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1514,6 +1510,13 @@
   <si>
     <t>15:05</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">2032년 발사되는 달착륙선(Korea Pathfinder Lunar Landr, KPLL)의 착륙후보지역에 대하여 착륙 및 운영 적합성 분석 작업 현황과 향후 수행 업무 등을 발표하고자 합니다. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다누리가 달 궤도 상에서 성공적으로 과학 임무를 수행하고 있다. 이러한 임무를 수행하기 위해 고려된 기계적인 형상에 대한 특징을 소개하며, 각 탑재체의 배치에 대한 개념도 소개하고자 한다.</t>
   </si>
 </sst>
 </file>
@@ -2017,10 +2020,10 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -2046,10 +2049,10 @@
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -2075,10 +2078,10 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -2104,10 +2107,10 @@
         <v>12</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="F6" t="s">
         <v>17</v>
@@ -2130,10 +2133,10 @@
         <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
@@ -2159,10 +2162,10 @@
         <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
@@ -2191,7 +2194,7 @@
         <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>101</v>
@@ -2223,7 +2226,7 @@
         <v>101</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
@@ -2233,6 +2236,9 @@
       </c>
       <c r="H11" t="s">
         <v>73</v>
+      </c>
+      <c r="I11" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -2246,10 +2252,10 @@
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="F12" t="s">
         <v>17</v>
@@ -2261,7 +2267,7 @@
         <v>103</v>
       </c>
       <c r="I12" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -2275,10 +2281,10 @@
         <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="F14" t="s">
         <v>15</v>
@@ -2304,10 +2310,10 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="F15" t="s">
         <v>15</v>
@@ -2333,10 +2339,10 @@
         <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="F16" t="s">
         <v>37</v>
@@ -2556,7 +2562,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B26" t="s">
         <v>22</v>

--- a/2026_Lunarworkshop_presentation.xlsx
+++ b/2026_Lunarworkshop_presentation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="151" documentId="8_{7C337711-845B-48E8-9B2F-7D4F6183F691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F741CD8-B016-4935-BEB4-B6F75B3D2666}"/>
+  <xr:revisionPtr revIDLastSave="152" documentId="8_{7C337711-845B-48E8-9B2F-7D4F6183F691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76BB53EA-F9DE-41B3-A2BB-D636B39D97B3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
   </bookViews>
@@ -141,10 +141,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>본 발표에서는 민간 달 착륙선 Intuitive Machines-3 (IM-3)에 탑재되어 달 표면으로 향하는 Lunar Space Environment Monitor (LUSEM)의 과학적 임무와 이를 통해 기대되는 연구 성과를 소개한다. LUSEM은 달 표면 및 주변 공간의 고에너지 입자를 관측하기 위해 개발된 탑재체로 Reiner Gamma  주변의 달 표면 우주환경을 이해하는 중요한 역할을 수행할  것으로 기대된다. 본 연구에서는 LUSEM의 개발 목적과 관측 메커니즘을 설명하고,  고에너지 입자 검출 시뮬레이션을 기반으로 도출된 초기 관측 기대 결과를 제시한다. LUSEM이 확보할 데이터는 달 표면의 전자기적 특성과 태양풍 및 지구 자기권과의 상호작용을 규명하는 데 기여할 것이며, 향후 유인 달 탐사 (아르테미스 계획 등)를 위한 우주 방사선 환경 예측 모델 수립에 필요한 기초 자료가 될 것으로 기대된다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>s8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1517,6 +1513,10 @@
   </si>
   <si>
     <t>다누리가 달 궤도 상에서 성공적으로 과학 임무를 수행하고 있다. 이러한 임무를 수행하기 위해 고려된 기계적인 형상에 대한 특징을 소개하며, 각 탑재체의 배치에 대한 개념도 소개하고자 한다.</t>
+  </si>
+  <si>
+    <t>본 연구는 2026년 말 발사 예정인 달 우주환경 센서(Lunar Space Environment Sensor, LUSEM) 임무를 중심으로, 순항·하강·착륙 후 등 탑재체 운용 단계별로 기대되는 과학적 성과를 분석한다. 아울러 현 임무 수행 시 발생할 수 있는 기술적 및 운용적 제약 요소를 도출하고, 이를 바탕으로 향후 추진될 유사 우주환경 관측 장비 개발 시 반영해야 할 핵심 과학적 요구사항(Scientific Requirements)을 정립하고자 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2020,10 +2020,10 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -2032,10 +2032,10 @@
         <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -2049,10 +2049,10 @@
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -2061,10 +2061,10 @@
         <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -2078,22 +2078,22 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
       <c r="G4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I4" t="s">
         <v>90</v>
-      </c>
-      <c r="H4" t="s">
-        <v>59</v>
-      </c>
-      <c r="I4" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -2107,19 +2107,19 @@
         <v>12</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="F6" t="s">
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -2133,22 +2133,22 @@
         <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -2162,22 +2162,22 @@
         <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -2185,7 +2185,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
@@ -2194,27 +2194,27 @@
         <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F10" t="s">
         <v>17</v>
       </c>
       <c r="G10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10" t="s">
         <v>75</v>
       </c>
-      <c r="H10" t="s">
-        <v>76</v>
-      </c>
       <c r="I10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
@@ -2223,27 +2223,27 @@
         <v>12</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
       </c>
       <c r="G11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
@@ -2252,27 +2252,27 @@
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="F12" t="s">
         <v>17</v>
       </c>
       <c r="G12" t="s">
+        <v>101</v>
+      </c>
+      <c r="H12" t="s">
         <v>102</v>
       </c>
-      <c r="H12" t="s">
-        <v>103</v>
-      </c>
       <c r="I12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
@@ -2281,27 +2281,27 @@
         <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="F14" t="s">
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" t="s">
         <v>11</v>
@@ -2310,27 +2310,27 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="F15" t="s">
         <v>15</v>
       </c>
       <c r="G15" t="s">
+        <v>46</v>
+      </c>
+      <c r="H15" t="s">
+        <v>63</v>
+      </c>
+      <c r="I15" t="s">
         <v>47</v>
-      </c>
-      <c r="H15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I15" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s">
         <v>11</v>
@@ -2339,27 +2339,27 @@
         <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="F16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" t="s">
+        <v>64</v>
+      </c>
+      <c r="I16" t="s">
         <v>40</v>
-      </c>
-      <c r="H16" t="s">
-        <v>65</v>
-      </c>
-      <c r="I16" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s">
         <v>22</v>
@@ -2368,27 +2368,27 @@
         <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="F18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G18" t="s">
+        <v>41</v>
+      </c>
+      <c r="H18" t="s">
+        <v>65</v>
+      </c>
+      <c r="I18" t="s">
         <v>42</v>
-      </c>
-      <c r="H18" t="s">
-        <v>66</v>
-      </c>
-      <c r="I18" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
@@ -2397,27 +2397,27 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F19" t="s">
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s">
         <v>22</v>
@@ -2426,27 +2426,27 @@
         <v>12</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F20" t="s">
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B21" t="s">
         <v>22</v>
@@ -2455,27 +2455,27 @@
         <v>12</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="F21" t="s">
         <v>17</v>
       </c>
       <c r="G21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
         <v>22</v>
@@ -2484,27 +2484,27 @@
         <v>12</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="F23" t="s">
         <v>16</v>
       </c>
       <c r="G23" t="s">
+        <v>50</v>
+      </c>
+      <c r="H23" t="s">
+        <v>68</v>
+      </c>
+      <c r="I23" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="H23" t="s">
-        <v>69</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B24" t="s">
         <v>22</v>
@@ -2513,27 +2513,27 @@
         <v>12</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F24" t="s">
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B25" t="s">
         <v>22</v>
@@ -2542,27 +2542,27 @@
         <v>12</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F25" t="s">
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B26" t="s">
         <v>22</v>
@@ -2571,19 +2571,19 @@
         <v>12</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="F26" t="s">
         <v>16</v>
       </c>
       <c r="G26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>21</v>

--- a/2026_Lunarworkshop_presentation.xlsx
+++ b/2026_Lunarworkshop_presentation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="152" documentId="8_{7C337711-845B-48E8-9B2F-7D4F6183F691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76BB53EA-F9DE-41B3-A2BB-D636B39D97B3}"/>
+  <xr:revisionPtr revIDLastSave="179" documentId="8_{7C337711-845B-48E8-9B2F-7D4F6183F691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6B265D6-E821-4A68-A517-81167321DAFF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
   </bookViews>
@@ -232,10 +232,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>11:15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>달 탐사용 자기장 측정기 개발 현황</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -362,26 +358,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10:45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11:45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>다누리 자기장 측정기 KMAG를 이용한 달 내부 구조 연구</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1452,26 +1428,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>16:25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16:40</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16:55</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>17:10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>17:25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>15:20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1516,6 +1472,50 @@
   </si>
   <si>
     <t>본 연구는 2026년 말 발사 예정인 달 우주환경 센서(Lunar Space Environment Sensor, LUSEM) 임무를 중심으로, 순항·하강·착륙 후 등 탑재체 운용 단계별로 기대되는 과학적 성과를 분석한다. 아울러 현 임무 수행 시 발생할 수 있는 기술적 및 운용적 제약 요소를 도출하고, 이를 바탕으로 향후 추진될 유사 우주환경 관측 장비 개발 시 반영해야 할 핵심 과학적 요구사항(Scientific Requirements)을 정립하고자 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17:05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:50</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2020,10 +2020,10 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -2032,10 +2032,10 @@
         <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I2" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -2049,10 +2049,10 @@
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -2061,10 +2061,10 @@
         <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -2078,22 +2078,22 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I4" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -2107,10 +2107,10 @@
         <v>12</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="F6" t="s">
         <v>17</v>
@@ -2119,7 +2119,7 @@
         <v>45</v>
       </c>
       <c r="H6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -2133,22 +2133,22 @@
         <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I7" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -2162,22 +2162,22 @@
         <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -2194,22 +2194,22 @@
         <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F10" t="s">
         <v>17</v>
       </c>
       <c r="G10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H10" t="s">
         <v>74</v>
       </c>
-      <c r="H10" t="s">
-        <v>75</v>
-      </c>
       <c r="I10" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -2223,22 +2223,22 @@
         <v>12</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G11" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="H11" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="I11" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -2252,22 +2252,22 @@
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F12" t="s">
         <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="H12" t="s">
-        <v>102</v>
-      </c>
-      <c r="I12" t="s">
-        <v>119</v>
+        <v>59</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -2281,10 +2281,10 @@
         <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F14" t="s">
         <v>15</v>
@@ -2293,10 +2293,10 @@
         <v>38</v>
       </c>
       <c r="H14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I14" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -2310,10 +2310,10 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F15" t="s">
         <v>15</v>
@@ -2322,7 +2322,7 @@
         <v>46</v>
       </c>
       <c r="H15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I15" t="s">
         <v>47</v>
@@ -2339,10 +2339,10 @@
         <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="F16" t="s">
         <v>36</v>
@@ -2351,7 +2351,7 @@
         <v>39</v>
       </c>
       <c r="H16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I16" t="s">
         <v>40</v>
@@ -2368,10 +2368,10 @@
         <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="F18" t="s">
         <v>36</v>
@@ -2380,7 +2380,7 @@
         <v>41</v>
       </c>
       <c r="H18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I18" t="s">
         <v>42</v>
@@ -2397,7 +2397,7 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>27</v>
@@ -2409,10 +2409,10 @@
         <v>44</v>
       </c>
       <c r="H19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I19" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -2429,7 +2429,7 @@
         <v>27</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F20" t="s">
         <v>15</v>
@@ -2438,10 +2438,10 @@
         <v>43</v>
       </c>
       <c r="H20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I20" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -2455,27 +2455,27 @@
         <v>12</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="F21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H21" t="s">
-        <v>60</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>94</v>
+        <v>71</v>
+      </c>
+      <c r="I21" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s">
         <v>22</v>
@@ -2484,27 +2484,27 @@
         <v>12</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="F23" t="s">
         <v>16</v>
       </c>
       <c r="G23" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I23" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="H23" t="s">
-        <v>68</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B24" t="s">
         <v>22</v>
@@ -2513,27 +2513,27 @@
         <v>12</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="F24" t="s">
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s">
         <v>22</v>
@@ -2542,27 +2542,27 @@
         <v>12</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="F25" t="s">
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B26" t="s">
         <v>22</v>
@@ -2571,19 +2571,19 @@
         <v>12</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="F26" t="s">
         <v>16</v>
       </c>
       <c r="G26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>21</v>

--- a/2026_Lunarworkshop_presentation.xlsx
+++ b/2026_Lunarworkshop_presentation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="179" documentId="8_{7C337711-845B-48E8-9B2F-7D4F6183F691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6B265D6-E821-4A68-A517-81167321DAFF}"/>
+  <xr:revisionPtr revIDLastSave="258" documentId="8_{7C337711-845B-48E8-9B2F-7D4F6183F691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BEE30FC6-2283-4BA9-AF1A-B223E383DDF0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="121">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1416,22 +1416,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>김동규(한국항공우주연구원)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>s21</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16:05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15:20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>13:20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1475,26 +1459,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>16:20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16:35</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16:50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>17:05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>17:20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>10:35</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1516,6 +1480,38 @@
   </si>
   <si>
     <t>11:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김동규 (한국항공우주연구원)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1968,7 +1964,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FAA5805-02C0-4AE9-B5DF-E91EE7468B4D}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="5" width="9" style="1"/>
@@ -2020,10 +2016,10 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -2035,7 +2031,7 @@
         <v>55</v>
       </c>
       <c r="I2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -2049,10 +2045,10 @@
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -2078,10 +2074,10 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -2096,29 +2092,29 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>18</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="D5" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F5" t="s">
         <v>17</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G5" t="s">
         <v>45</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H5" t="s">
         <v>60</v>
       </c>
     </row>
@@ -2133,22 +2129,22 @@
         <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="H7" t="s">
-        <v>58</v>
-      </c>
-      <c r="I7" t="s">
-        <v>82</v>
+        <v>59</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -2162,10 +2158,10 @@
         <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
@@ -2181,7 +2177,33 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="I9" s="2"/>
+      <c r="A9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I9" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -2194,7 +2216,7 @@
         <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>94</v>
@@ -2203,47 +2225,18 @@
         <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="H10" t="s">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="I10" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" t="s">
-        <v>95</v>
-      </c>
-      <c r="H11" t="s">
-        <v>96</v>
-      </c>
-      <c r="I11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
@@ -2252,22 +2245,51 @@
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F12" t="s">
         <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="H12" t="s">
-        <v>59</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>88</v>
+        <v>58</v>
+      </c>
+      <c r="I12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" t="s">
+        <v>61</v>
+      </c>
+      <c r="I13" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -2281,22 +2303,22 @@
         <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F14" t="s">
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I14" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -2310,51 +2332,51 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="G15" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I15" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>48</v>
       </c>
-      <c r="B16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="D17" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F17" t="s">
         <v>36</v>
       </c>
-      <c r="G16" t="s">
-        <v>39</v>
-      </c>
-      <c r="H16" t="s">
-        <v>63</v>
-      </c>
-      <c r="I16" t="s">
-        <v>40</v>
+      <c r="G17" t="s">
+        <v>41</v>
+      </c>
+      <c r="H17" t="s">
+        <v>64</v>
+      </c>
+      <c r="I17" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -2368,22 +2390,22 @@
         <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="F18" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I18" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -2397,22 +2419,22 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="F19" t="s">
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I19" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -2426,51 +2448,51 @@
         <v>12</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="F20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G20" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="H20" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I20" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>34</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" t="s">
         <v>22</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C22" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="D22" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F22" t="s">
         <v>16</v>
       </c>
-      <c r="G21" t="s">
-        <v>35</v>
-      </c>
-      <c r="H21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I21" t="s">
-        <v>109</v>
+      <c r="G22" t="s">
+        <v>49</v>
+      </c>
+      <c r="H22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
@@ -2484,22 +2506,22 @@
         <v>12</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="F23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s">
-        <v>67</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>50</v>
+        <v>68</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
@@ -2513,22 +2535,22 @@
         <v>12</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="F24" t="s">
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="H24" t="s">
-        <v>68</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>92</v>
+        <v>69</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
@@ -2542,52 +2564,26 @@
         <v>12</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="F25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G25" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="H25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>97</v>
-      </c>
-      <c r="B26" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="F26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G26" t="s">
-        <v>75</v>
-      </c>
-      <c r="H26" t="s">
-        <v>70</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>21</v>
-      </c>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I29" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/2026_Lunarworkshop_presentation.xlsx
+++ b/2026_Lunarworkshop_presentation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="258" documentId="8_{7C337711-845B-48E8-9B2F-7D4F6183F691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BEE30FC6-2283-4BA9-AF1A-B223E383DDF0}"/>
+  <xr:revisionPtr revIDLastSave="259" documentId="8_{7C337711-845B-48E8-9B2F-7D4F6183F691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6DD0BA2-402D-4997-91A3-4163966D1E5F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
   </bookViews>
@@ -1396,10 +1396,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>본 발표는 우리나라의 달탐사 계획과 앞으로의 방향성에 대한 초청 발표로, 20분의 발표 및 10분의 질의응답 시간으로 준비되어 있습니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>KMAG는 외부 자기장 변동에 대한 달 내부의 유도 자기장 응답을 분석하여 전기전도도 구조를 추정하는 전자기 탐사 기법을, 아폴로 시대 달 앞면 탐사에 이어 달 뒷면에 최초로 적용하였다. 이를 바탕으로 달 내부 구조와 진화 과정에 대한 새로운 제약 조건을 제시한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1512,6 +1508,10 @@
   </si>
   <si>
     <t>김동규 (한국항공우주연구원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>본 발표는 우리나라의 달탐사 계획과 앞으로의 방향성에 대한 초청 발표입니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2016,10 +2016,10 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -2031,7 +2031,7 @@
         <v>55</v>
       </c>
       <c r="I2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -2045,10 +2045,10 @@
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -2074,10 +2074,10 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -2103,10 +2103,10 @@
         <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
@@ -2129,10 +2129,10 @@
         <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
@@ -2158,10 +2158,10 @@
         <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
@@ -2178,7 +2178,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
@@ -2187,10 +2187,10 @@
         <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F9" t="s">
         <v>17</v>
@@ -2202,7 +2202,7 @@
         <v>74</v>
       </c>
       <c r="I9" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -2216,22 +2216,22 @@
         <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F10" t="s">
         <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -2245,10 +2245,10 @@
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="F12" t="s">
         <v>17</v>
@@ -2274,10 +2274,10 @@
         <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="F13" t="s">
         <v>15</v>
@@ -2303,10 +2303,10 @@
         <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="F14" t="s">
         <v>15</v>
@@ -2332,10 +2332,10 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="F15" t="s">
         <v>36</v>
@@ -2434,7 +2434,7 @@
         <v>66</v>
       </c>
       <c r="I19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -2451,7 +2451,7 @@
         <v>80</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F20" t="s">
         <v>16</v>
@@ -2463,7 +2463,7 @@
         <v>71</v>
       </c>
       <c r="I20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -2477,10 +2477,10 @@
         <v>12</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="F22" t="s">
         <v>16</v>
@@ -2506,10 +2506,10 @@
         <v>12</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="F23" t="s">
         <v>15</v>
@@ -2521,7 +2521,7 @@
         <v>68</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
@@ -2535,10 +2535,10 @@
         <v>12</v>
       </c>
       <c r="D24" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="F24" t="s">
         <v>15</v>
@@ -2564,10 +2564,10 @@
         <v>12</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="F25" t="s">
         <v>16</v>
